--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.02323</v>
+        <v>17.21464</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1799</v>
+        <v>16.57147</v>
       </c>
       <c r="E2" t="n">
-        <v>17.10058</v>
+        <v>16.93614</v>
       </c>
       <c r="F2" t="n">
-        <v>43.24103</v>
+        <v>42.67191</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05194</v>
+        <v>0.05074</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85765</v>
+        <v>1.84054</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.07428</v>
+        <v>17.16569</v>
       </c>
       <c r="D3" t="n">
-        <v>16.8974</v>
+        <v>16.83624</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81239</v>
+        <v>17.10786</v>
       </c>
       <c r="F3" t="n">
-        <v>43.22603</v>
+        <v>43.08031</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05041</v>
+        <v>0.05214</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84962</v>
+        <v>1.85445</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.98971</v>
+        <v>17.00984</v>
       </c>
       <c r="D4" t="n">
-        <v>16.83926</v>
+        <v>16.82624</v>
       </c>
       <c r="E4" t="n">
-        <v>16.84241</v>
+        <v>16.83961</v>
       </c>
       <c r="F4" t="n">
-        <v>43.78804</v>
+        <v>42.90503</v>
       </c>
       <c r="G4" t="n">
-        <v>0.051</v>
+        <v>0.05143</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81528</v>
+        <v>1.83737</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.96476</v>
+        <v>16.88051</v>
       </c>
       <c r="D5" t="n">
-        <v>16.73113</v>
+        <v>16.75119</v>
       </c>
       <c r="E5" t="n">
-        <v>16.69904</v>
+        <v>16.76044</v>
       </c>
       <c r="F5" t="n">
-        <v>42.61817</v>
+        <v>43.01604</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05147</v>
+        <v>0.0509</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83531</v>
+        <v>1.84934</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.97029</v>
+        <v>16.99429</v>
       </c>
       <c r="D6" t="n">
-        <v>16.86409</v>
+        <v>16.70116</v>
       </c>
       <c r="E6" t="n">
-        <v>17.10318</v>
+        <v>16.92842</v>
       </c>
       <c r="F6" t="n">
-        <v>42.7474</v>
+        <v>43.29914</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04929</v>
+        <v>0.05187</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86138</v>
+        <v>1.85995</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.94935</v>
+        <v>17.28425</v>
       </c>
       <c r="D7" t="n">
-        <v>16.88999</v>
+        <v>16.64928</v>
       </c>
       <c r="E7" t="n">
-        <v>17.16713</v>
+        <v>17.09179</v>
       </c>
       <c r="F7" t="n">
-        <v>42.50632</v>
+        <v>42.98966</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05117</v>
+        <v>0.05082</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8711</v>
+        <v>1.83902</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.42321</v>
+        <v>16.98869</v>
       </c>
       <c r="D8" t="n">
-        <v>16.77516</v>
+        <v>16.69589</v>
       </c>
       <c r="E8" t="n">
-        <v>16.97831</v>
+        <v>16.94627</v>
       </c>
       <c r="F8" t="n">
-        <v>42.96386</v>
+        <v>43.19953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05186</v>
+        <v>0.05201</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85195</v>
+        <v>1.84137</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.99471</v>
+        <v>16.98747</v>
       </c>
       <c r="D9" t="n">
-        <v>16.62342</v>
+        <v>16.60014</v>
       </c>
       <c r="E9" t="n">
-        <v>16.72682</v>
+        <v>16.69722</v>
       </c>
       <c r="F9" t="n">
-        <v>42.73241</v>
+        <v>43.39171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05087</v>
+        <v>0.05167</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88044</v>
+        <v>1.87796</v>
       </c>
     </row>
     <row r="10">
@@ -660,443 +660,712 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.19107</v>
+        <v>17.18964</v>
       </c>
       <c r="D10" t="n">
-        <v>16.65399</v>
+        <v>16.97419</v>
       </c>
       <c r="E10" t="n">
-        <v>16.85259</v>
+        <v>17.03999</v>
       </c>
       <c r="F10" t="n">
-        <v>43.18734</v>
+        <v>43.2173</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05144</v>
+        <v>0.05052</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85142</v>
+        <v>1.85676</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.87409</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.54442</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.84579</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.89241</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.823</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.02886</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.71293</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.9401</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.40323</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05254</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8198</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
-        </is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>17.0024</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.64172</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.64819</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.6974</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.85245</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
-        </is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>17.14541</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.69653</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.78296</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.50886</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05094</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8723</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
-        </is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>17.08303</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.78023</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.9395</v>
+      </c>
+      <c r="F15" t="n">
+        <v>43.6124</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.81508</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
-        </is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>17.21164</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.71539</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.79895</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.05808</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05152</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.85533</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
-        </is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16.87646</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.35278</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.65161</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.76767</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.81078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
-        </is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>16.98284</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.69039</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.82925</v>
+      </c>
+      <c r="F18" t="n">
+        <v>44.16201</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.85619</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
-        </is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17.05451</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.83063</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.97309</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.87651</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.85441</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.61866</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.15464</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.76845</v>
+        <v>0.61052</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07975</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.6121</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9720800000000001</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10984</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09637</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.1285</v>
+        <v>1.15264</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7680399999999999</v>
+        <v>0.61689</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08245</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.59661</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.97068</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11185</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12878</v>
+        <v>1.13664</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.74988</v>
+        <v>0.61313</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08155999999999999</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.59788</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9459</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11108</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09414</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12802</v>
+        <v>1.10881</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.76559</v>
+        <v>0.61307</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08074000000000001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.6081</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.99327</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.11165</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00766</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09353</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12634</v>
+        <v>1.13063</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.76709</v>
+        <v>0.62093</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08185000000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.61898</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.98365</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.10821</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09372</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12696</v>
+        <v>1.12374</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7672600000000001</v>
+        <v>0.61044</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08226</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.60595</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9782999999999999</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.10989</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09376</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12977</v>
+        <v>1.14145</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.75391</v>
+        <v>0.61542</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08297</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.6075</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.98121</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11225</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09540999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12816</v>
+        <v>1.15058</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.11408</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.76088</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.07903</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.61851</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.97534</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.10961</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09302000000000001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12577</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.74677</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08237999999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.60355</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.96993</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11073</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09458999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12917</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.76856</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08226</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6313299999999999</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.97782</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11231</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09361</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12688</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.77939</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.61777</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.98883</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09352000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12986</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.74951</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.07967</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.61779</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.97829</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11278</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09252000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12918</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.73366</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08117000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.62693</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10774</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09143</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12945</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7511100000000001</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08217000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.61849</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9770799999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11128</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09399</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.13154</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.75788</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.08129</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.6237200000000001</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.96939</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11057</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09279</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12768</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="C38" t="n">
+        <v>0.7557700000000001</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.60795</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.97184</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11099</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09474</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12751</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.75275</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.08114</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.61031</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10886</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09581000000000001</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12764</v>
+      <c r="C39" t="n">
+        <v>0.76853</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08425000000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6033500000000001</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.98886</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11134</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09425</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12941</v>
       </c>
     </row>
   </sheetData>
